--- a/results/reviews/2026-10-24/candidate_source_refresh/LATEST_verified_candidates.xlsx
+++ b/results/reviews/2026-10-24/candidate_source_refresh/LATEST_verified_candidates.xlsx
@@ -66005,7 +66005,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-24T03:20:22.177154-05:00</t>
+          <t>2026-10-24T12:42:32.188093-05:00</t>
         </is>
       </c>
     </row>
